--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486328_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486328_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.1762</v>
+        <v>7.2301</v>
       </c>
       <c r="E2" t="n">
-        <v>5.9279</v>
+        <v>5.7044</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2483</v>
+        <v>1.5257</v>
       </c>
       <c r="G2" t="n">
         <v>6.1417</v>
@@ -610,13 +610,13 @@
         <v>1.7401</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.375</v>
+        <v>-0.3212</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.2319</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3666</v>
+        <v>-0.0892</v>
       </c>
       <c r="V2" t="n">
         <v>-0.113</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. ARMUS</t>
+          <t>I. JAKOVICS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.1949</v>
+        <v>3.398</v>
       </c>
       <c r="E3" t="n">
-        <v>2.7955</v>
+        <v>3.4792</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3994</v>
+        <v>-0.08119999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>4.3596</v>
+        <v>1.9378</v>
       </c>
       <c r="H3" t="n">
-        <v>3.3365</v>
+        <v>2.4454</v>
       </c>
       <c r="I3" t="n">
-        <v>1.0231</v>
+        <v>-0.5076000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>4.4363</v>
+        <v>2.9779</v>
       </c>
       <c r="K3" t="n">
-        <v>3.6713</v>
+        <v>3.5102</v>
       </c>
       <c r="L3" t="n">
-        <v>0.765</v>
+        <v>-0.5323</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0767</v>
+        <v>-1.0401</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3348</v>
+        <v>-1.0648</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2582</v>
+        <v>0.0247</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.5225</v>
+        <v>1.5225</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.4801</v>
+        <v>-0.2175</v>
       </c>
       <c r="R3" t="n">
-        <v>1.9576</v>
+        <v>1.7401</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9058</v>
+        <v>-0.5143</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0791</v>
+        <v>0.1538</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1733</v>
+        <v>-0.6682</v>
       </c>
       <c r="V3" t="n">
         <v>0.452</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7602</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.3082</v>
+        <v>-0.113</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. JAKOVICS</t>
+          <t>M. ARMUS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.6331</v>
+        <v>3.1544</v>
       </c>
       <c r="E4" t="n">
-        <v>3.591</v>
+        <v>2.1249</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0421</v>
+        <v>1.0295</v>
       </c>
       <c r="G4" t="n">
-        <v>1.9378</v>
+        <v>4.3596</v>
       </c>
       <c r="H4" t="n">
-        <v>2.4454</v>
+        <v>3.3365</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5076000000000001</v>
+        <v>1.0231</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9779</v>
+        <v>4.4363</v>
       </c>
       <c r="K4" t="n">
-        <v>3.5102</v>
+        <v>3.6713</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5323</v>
+        <v>0.765</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.0401</v>
+        <v>-0.0767</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.0648</v>
+        <v>-0.3348</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0247</v>
+        <v>0.2582</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5225</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2175</v>
+        <v>-3.4801</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7401</v>
+        <v>1.9576</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2793</v>
+        <v>-0.1346</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2656</v>
+        <v>0.4086</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5449000000000001</v>
+        <v>-0.5432</v>
       </c>
       <c r="V4" t="n">
         <v>0.452</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.7602</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.113</v>
+        <v>-0.3082</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2462</v>
+        <v>0.5083</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.0402</v>
+        <v>-1.5932</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2864</v>
+        <v>2.1014</v>
       </c>
       <c r="G5" t="n">
         <v>-1.6015</v>
@@ -844,13 +844,13 @@
         <v>1.305</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0224</v>
+        <v>0.2397</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4795</v>
+        <v>-0.0324</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4571</v>
+        <v>0.2722</v>
       </c>
       <c r="V5" t="n">
         <v>0.5649999999999999</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. RODRIGUEZ BARRIENTOS</t>
+          <t>X. OROZ URIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3916</v>
+        <v>0.1839</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9323</v>
+        <v>0.6705</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5407</v>
+        <v>-0.4865</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.1093</v>
+        <v>0.2554</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5778</v>
+        <v>-0.6267</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5315</v>
+        <v>0.8821</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.4719</v>
+        <v>0.7282</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.7268</v>
+        <v>0.0397</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.7451</v>
+        <v>0.6885</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3626</v>
+        <v>-0.4727</v>
       </c>
       <c r="N6" t="n">
-        <v>0.149</v>
+        <v>-0.6663</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2136</v>
+        <v>0.1936</v>
       </c>
       <c r="P6" t="n">
-        <v>0.435</v>
+        <v>0.87</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.435</v>
+        <v>0.87</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2826</v>
+        <v>-0.9415</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5396</v>
+        <v>-0.0577</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2569</v>
+        <v>-0.8839</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X. OROZ URIA</t>
+          <t>A. KUNKEL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5598</v>
+        <v>-0.2323</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1117</v>
+        <v>1.758</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6715</v>
+        <v>-1.9904</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2554</v>
+        <v>4.187</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6267</v>
+        <v>2.7798</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8821</v>
+        <v>1.4073</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7282</v>
+        <v>4.9291</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0397</v>
+        <v>3.3975</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6885</v>
+        <v>1.5316</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4727</v>
+        <v>-0.7421</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6663</v>
+        <v>-0.6178</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1936</v>
+        <v>-0.1243</v>
       </c>
       <c r="P7" t="n">
-        <v>0.87</v>
+        <v>-1.9576</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-3.4801</v>
       </c>
       <c r="R7" t="n">
-        <v>0.87</v>
+        <v>1.5225</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.6853</v>
+        <v>-1.3934</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6165</v>
+        <v>-0.256</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.0688</v>
+        <v>-1.1374</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.0684</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.6334</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. KUNKEL</t>
+          <t>T. BORG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6408</v>
+        <v>-0.2377</v>
       </c>
       <c r="E8" t="n">
-        <v>1.5345</v>
+        <v>1.602</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.1753</v>
+        <v>-1.8397</v>
       </c>
       <c r="G8" t="n">
-        <v>4.187</v>
+        <v>2.7058</v>
       </c>
       <c r="H8" t="n">
-        <v>2.7798</v>
+        <v>-0.9885</v>
       </c>
       <c r="I8" t="n">
-        <v>1.4073</v>
+        <v>3.6942</v>
       </c>
       <c r="J8" t="n">
-        <v>4.9291</v>
+        <v>3.741</v>
       </c>
       <c r="K8" t="n">
-        <v>3.3975</v>
+        <v>-0.5046</v>
       </c>
       <c r="L8" t="n">
-        <v>1.5316</v>
+        <v>4.2457</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.7421</v>
+        <v>-1.0353</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6178</v>
+        <v>-0.4838</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1243</v>
+        <v>-0.5514</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.9576</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.4801</v>
+        <v>-2.1751</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5225</v>
+        <v>1.0875</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.8018</v>
+        <v>0.0342</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4795</v>
+        <v>0.0361</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.3224</v>
+        <v>-0.0018</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0684</v>
+        <v>-1.8902</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.6334</v>
+        <v>-1.8902</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. GONZALEZ CALVO</t>
+          <t>M. RODRIGUEZ BARRIENTOS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7359</v>
+        <v>-0.6653</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4122</v>
+        <v>-1.2676</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3236</v>
+        <v>0.6022999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0166</v>
+        <v>-1.1093</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2222</v>
+        <v>-0.5778</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2056</v>
+        <v>-0.5315</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2042</v>
+        <v>-1.4719</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1277</v>
+        <v>-0.7268</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0765</v>
+        <v>-0.7451</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2208</v>
+        <v>0.3626</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3499</v>
+        <v>0.149</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1291</v>
+        <v>0.2136</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.87</v>
+        <v>0.435</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2175</v>
+        <v>0.435</v>
       </c>
       <c r="S9" t="n">
-        <v>0.346</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4711</v>
+        <v>0.2043</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1251</v>
+        <v>-0.1953</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T. BORG</t>
+          <t>J. GONZALEZ CALVO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7464</v>
+        <v>-1.102</v>
       </c>
       <c r="E10" t="n">
-        <v>1.155</v>
+        <v>-0.7475000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.9014</v>
+        <v>-0.3545</v>
       </c>
       <c r="G10" t="n">
-        <v>2.7058</v>
+        <v>-0.0166</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9885</v>
+        <v>-0.2222</v>
       </c>
       <c r="I10" t="n">
-        <v>3.6942</v>
+        <v>0.2056</v>
       </c>
       <c r="J10" t="n">
-        <v>3.741</v>
+        <v>0.2042</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5046</v>
+        <v>0.1277</v>
       </c>
       <c r="L10" t="n">
-        <v>4.2457</v>
+        <v>0.0765</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.0353</v>
+        <v>-0.2208</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4838</v>
+        <v>-0.3499</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5514</v>
+        <v>0.1291</v>
       </c>
       <c r="P10" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="Q10" t="n">
         <v>-1.0875</v>
       </c>
-      <c r="Q10" t="n">
-        <v>-2.1751</v>
-      </c>
       <c r="R10" t="n">
-        <v>1.0875</v>
+        <v>0.2175</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4744</v>
+        <v>-0.0201</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.411</v>
+        <v>0.1358</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0635</v>
+        <v>-0.1559</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.8902</v>
+        <v>-0.1952</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.8902</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.1695</v>
+        <v>-1.3852</v>
       </c>
       <c r="E11" t="n">
         <v>0.3928</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.5623</v>
+        <v>-1.778</v>
       </c>
       <c r="G11" t="n">
         <v>-0.7466</v>
@@ -1312,13 +1312,13 @@
         <v>1.305</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8324</v>
+        <v>-1.0482</v>
       </c>
       <c r="T11" t="n">
         <v>-0.0769</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7554999999999999</v>
+        <v>-0.9713000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>-0.678</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.9675</v>
+        <v>-1.8134</v>
       </c>
       <c r="E12" t="n">
         <v>-2.6658</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6983</v>
+        <v>0.8524</v>
       </c>
       <c r="G12" t="n">
         <v>1.2145</v>
@@ -1390,13 +1390,13 @@
         <v>0.87</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5942</v>
+        <v>-0.4401</v>
       </c>
       <c r="T12" t="n">
         <v>-0.1454</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4488</v>
+        <v>-0.2947</v>
       </c>
       <c r="V12" t="n">
         <v>-0.1952</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.038900000000002</v>
+        <v>9.038800000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>9.457899999999999</v>
+        <v>9.457699999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4188999999999993</v>
+        <v>-0.419</v>
       </c>
       <c r="G13" t="n">
         <v>17.3278</v>
       </c>
       <c r="H13" t="n">
-        <v>6.052499999999999</v>
+        <v>6.0525</v>
       </c>
       <c r="I13" t="n">
         <v>11.2754</v>
@@ -1468,13 +1468,13 @@
         <v>13.0503</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.5304</v>
+        <v>-4.5305</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1382</v>
+        <v>0.1383000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.6687</v>
+        <v>-4.668699999999999</v>
       </c>
       <c r="V13" t="n">
         <v>-2.671</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.0955</v>
+        <v>3.6234</v>
       </c>
       <c r="E14" t="n">
-        <v>3.6603</v>
+        <v>4.2191</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5649</v>
+        <v>-0.5957</v>
       </c>
       <c r="G14" t="n">
         <v>3.7547</v>
@@ -1546,13 +1546,13 @@
         <v>2.3926</v>
       </c>
       <c r="S14" t="n">
-        <v>0.632</v>
+        <v>1.1599</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6682</v>
+        <v>1.2269</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0362</v>
+        <v>-0.067</v>
       </c>
       <c r="V14" t="n">
         <v>-0.4212</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.2314</v>
+        <v>2.2199</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6074</v>
+        <v>1.7192</v>
       </c>
       <c r="F15" t="n">
-        <v>0.624</v>
+        <v>0.5007</v>
       </c>
       <c r="G15" t="n">
         <v>1.1304</v>
@@ -1624,13 +1624,13 @@
         <v>1.0875</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3408</v>
+        <v>0.3293</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3341</v>
+        <v>0.4458</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0067</v>
+        <v>-0.1166</v>
       </c>
       <c r="V15" t="n">
         <v>0.7602</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. COSIALLS BORRAS</t>
+          <t>G. PARHAM II</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9166</v>
+        <v>1.8132</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6258</v>
+        <v>4.204</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.7092000000000001</v>
+        <v>-2.3908</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.8802</v>
+        <v>-1.7632</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.4842</v>
+        <v>0.2098</v>
       </c>
       <c r="I16" t="n">
-        <v>0.604</v>
+        <v>-1.973</v>
       </c>
       <c r="J16" t="n">
-        <v>1.3496</v>
+        <v>1.9154</v>
       </c>
       <c r="K16" t="n">
-        <v>0.2587</v>
+        <v>2.105</v>
       </c>
       <c r="L16" t="n">
-        <v>1.0909</v>
+        <v>-0.1896</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.2298</v>
+        <v>-3.6786</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.7429</v>
+        <v>-1.8952</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4869</v>
+        <v>-1.7834</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2175</v>
+        <v>1.5225</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.305</v>
+        <v>1.5225</v>
       </c>
       <c r="S16" t="n">
-        <v>2.2096</v>
+        <v>0.5849</v>
       </c>
       <c r="T16" t="n">
-        <v>2.3638</v>
+        <v>0.5936</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1542</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3698</v>
+        <v>1.469</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.695</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3698</v>
+        <v>-0.226</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. PARHAM II</t>
+          <t>R. COSIALLS BORRAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1118</v>
+        <v>0.7913</v>
       </c>
       <c r="E17" t="n">
-        <v>3.5334</v>
+        <v>1.2847</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.4216</v>
+        <v>-0.4934</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.7632</v>
+        <v>-0.8802</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2098</v>
+        <v>-1.4842</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.973</v>
+        <v>0.604</v>
       </c>
       <c r="J17" t="n">
-        <v>1.9154</v>
+        <v>1.3496</v>
       </c>
       <c r="K17" t="n">
-        <v>2.105</v>
+        <v>0.2587</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.1896</v>
+        <v>1.0909</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.6786</v>
+        <v>-2.2298</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.8952</v>
+        <v>-1.7429</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.7834</v>
+        <v>-0.4869</v>
       </c>
       <c r="P17" t="n">
-        <v>1.5225</v>
+        <v>0.2175</v>
       </c>
       <c r="Q17" t="n">
+        <v>-1.0875</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.305</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.0842</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.0227</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.0616</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.3698</v>
+      </c>
+      <c r="W17" t="n">
         <v>0</v>
       </c>
-      <c r="R17" t="n">
-        <v>1.5225</v>
-      </c>
-      <c r="S17" t="n">
-        <v>-0.1164</v>
-      </c>
-      <c r="T17" t="n">
-        <v>-0.0769</v>
-      </c>
-      <c r="U17" t="n">
-        <v>-0.0395</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.469</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.695</v>
-      </c>
       <c r="X17" t="n">
-        <v>-0.226</v>
+        <v>0.3698</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4439</v>
+        <v>-0.575</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8226</v>
+        <v>0.5991</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2666</v>
+        <v>-1.1741</v>
       </c>
       <c r="G18" t="n">
         <v>-2.9804</v>
@@ -1858,13 +1858,13 @@
         <v>1.5225</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8187</v>
+        <v>0.6877</v>
       </c>
       <c r="T18" t="n">
-        <v>1.0106</v>
+        <v>0.7871</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1919</v>
+        <v>-0.0994</v>
       </c>
       <c r="V18" t="n">
         <v>0.1952</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. FAURE RIBES</t>
+          <t>D. DUSCAK</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.7591</v>
+        <v>-1.8191</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4909</v>
+        <v>0.2161</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.25</v>
+        <v>-2.0352</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.653</v>
+        <v>-2.5013</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1612</v>
+        <v>-1.0312</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.4917</v>
+        <v>-1.4702</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4429</v>
+        <v>0.0464</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4047</v>
+        <v>-0.0333</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0382</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.0959</v>
+        <v>-2.5477</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5659</v>
+        <v>-0.9978</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.53</v>
+        <v>-1.5499</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2175</v>
+        <v>0.87</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2175</v>
+        <v>1.9576</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4881</v>
+        <v>-0.0132</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3425</v>
+        <v>-0.2632</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1456</v>
+        <v>0.2499</v>
       </c>
       <c r="V19" t="n">
-        <v>0.1645</v>
+        <v>-0.1745</v>
       </c>
       <c r="W19" t="n">
-        <v>0.3904</v>
+        <v>1.5204</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.226</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. LOBACO MUÑOZ</t>
+          <t>A. FAURE RIBES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2261</v>
+        <v>-1.8208</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.901</v>
+        <v>0.4909</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3251</v>
+        <v>-2.3116</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.3325</v>
+        <v>-1.653</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.6789</v>
+        <v>-0.1612</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.6535</v>
+        <v>-1.4917</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.6013</v>
+        <v>0.4429</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4808</v>
+        <v>0.4047</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.0822</v>
+        <v>0.0382</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.7311</v>
+        <v>-2.0959</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.1598</v>
+        <v>-0.5659</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5714</v>
+        <v>-1.53</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.6525</v>
+        <v>0.2175</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5225</v>
+        <v>0.2175</v>
       </c>
       <c r="S20" t="n">
-        <v>1.6597</v>
+        <v>-0.5498</v>
       </c>
       <c r="T20" t="n">
-        <v>1.5502</v>
+        <v>-0.3425</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1095</v>
+        <v>-0.2073</v>
       </c>
       <c r="V20" t="n">
-        <v>1.0992</v>
+        <v>0.1645</v>
       </c>
       <c r="W20" t="n">
-        <v>1.3252</v>
+        <v>0.3904</v>
       </c>
       <c r="X20" t="n">
         <v>-0.226</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. DUSCAK</t>
+          <t>R. LOBACO MUÑOZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.5011</v>
+        <v>-2.4188</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3427</v>
+        <v>-1.1245</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.1585</v>
+        <v>-1.2943</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.5013</v>
+        <v>-4.3325</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.0312</v>
+        <v>-1.6789</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.4702</v>
+        <v>-2.6535</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0464</v>
+        <v>-1.6013</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.0333</v>
+        <v>0.4808</v>
       </c>
       <c r="L21" t="n">
-        <v>0.07969999999999999</v>
+        <v>-2.0822</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.5477</v>
+        <v>-2.7311</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.9978</v>
+        <v>-2.1598</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.5499</v>
+        <v>-0.5714</v>
       </c>
       <c r="P21" t="n">
-        <v>0.87</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R21" t="n">
-        <v>1.9576</v>
+        <v>1.5225</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6953</v>
+        <v>1.467</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.822</v>
+        <v>1.3267</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1267</v>
+        <v>0.1403</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.1745</v>
+        <v>1.0992</v>
       </c>
       <c r="W21" t="n">
-        <v>1.5204</v>
+        <v>1.3252</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.695</v>
+        <v>-0.226</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.4068</v>
+        <v>-4.8962</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.4773</v>
+        <v>-5.8125</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0705</v>
+        <v>0.9163</v>
       </c>
       <c r="G22" t="n">
         <v>-5.5441</v>
@@ -2170,13 +2170,13 @@
         <v>1.5225</v>
       </c>
       <c r="S22" t="n">
-        <v>0.9283</v>
+        <v>0.4389</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5997</v>
+        <v>0.2644</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3287</v>
+        <v>0.1745</v>
       </c>
       <c r="V22" t="n">
         <v>-0.226</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.0571</v>
+        <v>-5.9569</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.6006</v>
+        <v>-5.377</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.4565</v>
+        <v>-0.5798</v>
       </c>
       <c r="G23" t="n">
         <v>-2.5583</v>
@@ -2248,13 +2248,13 @@
         <v>1.0875</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7588</v>
+        <v>-0.6585</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6165</v>
+        <v>-0.3929</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1423</v>
+        <v>-0.2656</v>
       </c>
       <c r="V23" t="n">
         <v>-0.5649999999999999</v>
@@ -2281,10 +2281,10 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-9.0388</v>
+        <v>-9.039</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4188000000000009</v>
+        <v>0.4190999999999994</v>
       </c>
       <c r="F24" t="n">
         <v>-9.4579</v>
@@ -2326,13 +2326,13 @@
         <v>14.1377</v>
       </c>
       <c r="S24" t="n">
-        <v>4.5305</v>
+        <v>4.5304</v>
       </c>
       <c r="T24" t="n">
-        <v>4.668699999999999</v>
+        <v>4.6686</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1381</v>
+        <v>-0.1383</v>
       </c>
       <c r="V24" t="n">
         <v>2.6712</v>
